--- a/266_extrato_conciliacao.xlsx
+++ b/266_extrato_conciliacao.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tarifas'!$12:$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Tarifas'!$B$1:$E$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Aplicacoes'!$12:$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Aplicacoes'!$B$1:$E$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Aplicacoes'!$B$1:$E$66</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Geral'!$12:$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Geral'!$B$1:$E$71</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,11 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -99,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -154,6 +159,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+    </border>
     <border>
       <left/>
       <right style="thin">
@@ -187,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -234,11 +245,16 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -724,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C26"/>
+  <dimension ref="B2:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -883,7 +899,7 @@
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>APLICAÇÂO AUTOMATICA</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -908,11 +924,69 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Saldo Inicial:</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Saldo Final:</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Indefinido2</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Saldo Inicial:</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Saldo Final:</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B12:C12"/>
@@ -930,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E21"/>
+  <dimension ref="B2:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -962,11 +1036,6 @@
           <t>Agência/Conta:</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0758/0005354-0</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
@@ -977,6 +1046,11 @@
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>01/01/2026 até 31/01/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0758/0005354-0</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E42"/>
+  <dimension ref="B2:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1356,14 +1430,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>GRUPO: APLICAÇÂO AUTOMATICA</t>
         </is>
       </c>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="24" t="n"/>
+      <c r="E23" s="22" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="14" t="inlineStr">
@@ -1378,12 +1450,7 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Aplicação (R$)</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Resgate (R$)</t>
+          <t>Rendimento</t>
         </is>
       </c>
     </row>
@@ -1398,10 +1465,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="21" t="n">
+      <c r="D25" s="21" t="n">
         <v>0.96</v>
       </c>
+      <c r="E25" s="23" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="15" t="inlineStr">
@@ -1414,10 +1481,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="21" t="n">
+      <c r="D26" s="21" t="n">
         <v>0.91</v>
       </c>
+      <c r="E26" s="23" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="15" t="inlineStr">
@@ -1430,10 +1497,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="21" t="n">
+      <c r="D27" s="21" t="n">
         <v>0.01</v>
       </c>
+      <c r="E27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="15" t="inlineStr">
@@ -1446,10 +1513,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="21" t="n">
+      <c r="D28" s="21" t="n">
         <v>0.02</v>
       </c>
+      <c r="E28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="15" t="inlineStr">
@@ -1462,10 +1529,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="21" t="n">
+      <c r="D29" s="21" t="n">
         <v>0.02</v>
       </c>
+      <c r="E29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="15" t="inlineStr">
@@ -1478,10 +1545,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="21" t="n">
+      <c r="D30" s="21" t="n">
         <v>0.04</v>
       </c>
+      <c r="E30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="15" t="inlineStr">
@@ -1494,10 +1561,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="21" t="n">
+      <c r="D31" s="21" t="n">
         <v>0.77</v>
       </c>
+      <c r="E31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="15" t="inlineStr">
@@ -1510,10 +1577,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="21" t="n">
+      <c r="D32" s="21" t="n">
         <v>0.14</v>
       </c>
+      <c r="E32" s="23" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="15" t="inlineStr">
@@ -1526,10 +1593,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="21" t="n">
+      <c r="D33" s="21" t="n">
         <v>0.68</v>
       </c>
+      <c r="E33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="15" t="inlineStr">
@@ -1542,10 +1609,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="21" t="n">
+      <c r="D34" s="21" t="n">
         <v>3.07</v>
       </c>
+      <c r="E34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="15" t="inlineStr">
@@ -1558,10 +1625,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="21" t="n">
+      <c r="D35" s="21" t="n">
         <v>1.01</v>
       </c>
+      <c r="E35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="15" t="inlineStr">
@@ -1574,10 +1641,10 @@
           <t>RENDIMENTOS REND PAGO APLIC AUT MAIS</t>
         </is>
       </c>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="21" t="n">
+      <c r="D36" s="21" t="n">
         <v>0.23</v>
       </c>
+      <c r="E36" s="23" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="18" t="inlineStr">
@@ -1590,54 +1657,282 @@
         <f>SUM(D25:D36)</f>
         <v/>
       </c>
-      <c r="E37" s="19">
-        <f>SUM(E25:E36)</f>
+    </row>
+    <row r="39">
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>GRUPO: CDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Aplicação (R$)</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Resgate (R$)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>Sem registros</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="19">
+        <f>SUM(D41:D42)</f>
         <v/>
       </c>
-    </row>
-    <row r="38">
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E43" s="19">
+        <f>SUM(E41:E42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Saldo Inicial:</t>
         </is>
       </c>
-      <c r="E38" s="10">
+      <c r="E44" s="10">
         <f>Resumo!C25</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="D39" s="2" t="inlineStr">
+    <row r="45">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Saldo Final:</t>
         </is>
       </c>
-      <c r="E39" s="10">
+      <c r="E45" s="10">
         <f>Resumo!C26</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="D40" s="2" t="inlineStr">
+    <row r="46">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Rendimento:</t>
         </is>
       </c>
-      <c r="E40" s="10">
-        <f>Resumo!C26-(Resumo!C25+(-D37)-E37)</f>
+      <c r="E46" s="10">
+        <f>Resumo!C26-(Resumo!C25+(-D43)-E43)</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="E42" s="5" t="n"/>
+    <row r="48">
+      <c r="B48" s="25">
+        <f>"GRUPO: "&amp;Resumo!B28</f>
+        <v/>
+      </c>
+      <c r="C48" s="26" t="n"/>
+      <c r="D48" s="26" t="n"/>
+      <c r="E48" s="27" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Aplicação (R$)</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Resgate (R$)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>Sem registros</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="19">
+        <f>SUM(D50:D51)</f>
+        <v/>
+      </c>
+      <c r="E52" s="19">
+        <f>SUM(E50:E51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Saldo Inicial:</t>
+        </is>
+      </c>
+      <c r="E53" s="10">
+        <f>Resumo!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Saldo Final:</t>
+        </is>
+      </c>
+      <c r="E54" s="10">
+        <f>Resumo!C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Rendimento:</t>
+        </is>
+      </c>
+      <c r="E55" s="10">
+        <f>Resumo!C30-(Resumo!C29+(-D52)-E52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="25">
+        <f>"GRUPO: "&amp;Resumo!B32</f>
+        <v/>
+      </c>
+      <c r="C57" s="26" t="n"/>
+      <c r="D57" s="26" t="n"/>
+      <c r="E57" s="27" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Aplicação (R$)</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>Resgate (R$)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>Sem registros</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="19">
+        <f>SUM(D59:D60)</f>
+        <v/>
+      </c>
+      <c r="E61" s="19">
+        <f>SUM(E59:E60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Saldo Inicial:</t>
+        </is>
+      </c>
+      <c r="E62" s="10">
+        <f>Resumo!C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Saldo Final:</t>
+        </is>
+      </c>
+      <c r="E63" s="10">
+        <f>Resumo!C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Rendimento:</t>
+        </is>
+      </c>
+      <c r="E64" s="10">
+        <f>Resumo!C34-(Resumo!C33+(-D61)-E61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B23:E23"/>
+  <mergeCells count="11">
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B39:E39"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1652,7 +1947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E70"/>
+  <dimension ref="B2:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1684,11 +1979,6 @@
           <t>Agência/Conta:</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0758/0005354-0</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
@@ -1699,6 +1989,11 @@
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>01/01/2026 até 31/01/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0758/0005354-0</t>
         </is>
       </c>
     </row>
@@ -1819,10 +2114,6 @@
         <f>SUM(D13:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="19">
-        <f>SUM(E13:E17)</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="B19" s="13" t="inlineStr">
@@ -2517,10 +2808,6 @@
       <c r="C66" s="4" t="n"/>
       <c r="D66" s="19">
         <f>SUM(D22:D65)</f>
-        <v/>
-      </c>
-      <c r="E66" s="19">
-        <f>SUM(E22:E65)</f>
         <v/>
       </c>
     </row>
